--- a/dados/log_execucoes.xlsx
+++ b/dados/log_execucoes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="execucoes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'execucoes'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'execucoes'!$A$1:$G$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,7 +1110,6 @@
           <t>Processador AMD Ryzen 5 5600</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1139,7 +1138,6 @@
           <t>Placa de Vídeo GeForce RTX 5060 8GB; Placa de Vídeo GeForce RTX 5070 12GB; Placa de Vídeo GeForce RTX 3060 12GB</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1168,7 +1166,6 @@
           <t>Processador AMD Ryzen 5 5600; Processador AMD Ryzen 7 7800X3D</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1197,10 +1194,237 @@
           <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz; Placa-mãe ASUS TUF Gaming B550M-Plus; Fonte Corsair CX650 650W 80 Plus Bronze; Fonte XPG Core Reactor II VE 750W 80 Plus Gold</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46313.53574074074</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46313.53574074074</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pichau</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Memória RAM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SEM_DADOS</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz; Memória Kingston Fury Beast 16GB DDR4 3200MHz; Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nenhum produto do catálogo encontrado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46313.53574074074</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Terabyte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46313.53574074074</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Página de bloqueio/desafio em https://www.amazon.com.br/s?k=processador+ryzen+5+5600 (título: 'Amazon.com.br Algo deu errado')</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46313.53934027778</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46313.53934027778</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pichau</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB M.2 NVMe; SSD Kingston A400 480GB SATA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46313.53934027778</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Terabyte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Memória RAM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz; Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46313.53934027778</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>17</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz; Placa-mãe ASUS TUF Gaming B550M-Plus; Fonte Corsair CX650 650W 80 Plus Bronze; Fonte XPG Core Reactor II VE 750W 80 Plus Gold</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G27"/>
+  <autoFilter ref="A1:G35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados/log_execucoes.xlsx
+++ b/dados/log_execucoes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="execucoes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="execucoes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'execucoes'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'execucoes'!$A$1:$G$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1334,7 +1334,6 @@
           <t>Processador AMD Ryzen 5 5600</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1363,7 +1362,6 @@
           <t>SSD Samsung 990 Pro 1TB M.2 NVMe; SSD Kingston A400 480GB SATA</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1392,7 +1390,6 @@
           <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz; Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1421,10 +1418,237 @@
           <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz; Placa-mãe ASUS TUF Gaming B550M-Plus; Fonte Corsair CX650 650W 80 Plus Bronze; Fonte XPG Core Reactor II VE 750W 80 Plus Gold</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46314.12502314815</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46314.12502314815</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pichau</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Processador</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600; Processador AMD Ryzen 5 7600; Processador Intel Core i5-12400F; Processador Intel Core i5-14400F</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46314.12502314815</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Terabyte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46314.12502314815</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Página de bloqueio/desafio em https://www.amazon.com.br/s?k=processador+ryzen+5+5600 (título: 'Amazon.com.br Algo deu errado')</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46314.46238425926</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>20</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46314.46238425926</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pichau</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5060 8GB; Placa de Vídeo GeForce RTX 5070 12GB; Placa de Vídeo GeForce RTX 3060 12GB</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46314.46238425926</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Terabyte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Placa-mãe</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Placa-mãe MSI PRO B650M-P</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46314.46238425926</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Página de bloqueio/desafio em https://www.amazon.com.br/s?k=processador+ryzen+5+5600 (título: 'Amazon.com.br Algo deu errado')</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G35"/>
+  <autoFilter ref="A1:G43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>